--- a/frontend/public/ejemplos/nomina_beneficios/RQ-004_mayor_de_gasto_de_nomina.xlsx
+++ b/frontend/public/ejemplos/nomina_beneficios/RQ-004_mayor_de_gasto_de_nomina.xlsx
@@ -660,25 +660,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -693,25 +693,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -726,25 +726,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -759,25 +759,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,25 +792,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -825,25 +825,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -858,25 +858,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1089,25 +1089,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1122,25 +1122,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1155,25 +1155,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1188,25 +1188,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1221,25 +1221,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1254,25 +1254,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1287,25 +1287,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1518,25 +1518,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1551,25 +1551,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1584,25 +1584,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1617,25 +1617,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1650,25 +1650,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1683,25 +1683,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1716,25 +1716,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1947,25 +1947,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1980,25 +1980,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2013,25 +2013,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2046,25 +2046,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2079,25 +2079,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2112,25 +2112,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2145,25 +2145,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2376,25 +2376,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2409,25 +2409,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2442,25 +2442,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2475,25 +2475,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2508,25 +2508,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2541,25 +2541,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2574,25 +2574,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2805,25 +2805,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,25 +2838,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2871,25 +2871,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2904,25 +2904,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2937,25 +2937,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2970,25 +2970,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3003,25 +3003,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3234,25 +3234,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3267,25 +3267,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3300,25 +3300,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3333,25 +3333,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3366,25 +3366,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3399,25 +3399,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3432,25 +3432,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3663,25 +3663,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3696,25 +3696,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3729,25 +3729,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3762,25 +3762,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3795,25 +3795,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3828,25 +3828,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3861,25 +3861,25 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4092,25 +4092,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4125,25 +4125,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4158,25 +4158,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4191,25 +4191,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4224,25 +4224,25 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4257,25 +4257,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4290,25 +4290,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4521,25 +4521,25 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4554,25 +4554,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4587,25 +4587,25 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4620,25 +4620,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4653,25 +4653,25 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4686,25 +4686,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4719,25 +4719,25 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4950,25 +4950,25 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -4983,25 +4983,25 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5016,25 +5016,25 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5049,25 +5049,25 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5082,25 +5082,25 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5115,25 +5115,25 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5148,25 +5148,25 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5379,25 +5379,25 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5PYG.51070.001</t>
+          <t>5PYG.51080.001</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Bono Desempeño</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5412,25 +5412,25 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5PYG.51070.002</t>
+          <t>5PYG.51090.001</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Comisiones</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5445,25 +5445,25 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5PYG.51080.001</t>
+          <t>5PYG.51100.001</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bono Desempeño</t>
+          <t>Premios</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5478,25 +5478,25 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5PYG.51090.001</t>
+          <t>5PYG.51110.001</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Comisiones</t>
+          <t>Estipendio Pasantes</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5511,25 +5511,25 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5PYG.51100.001</t>
+          <t>5PYG.51120.001</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>20</v>
+        <v>82.72</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Premios</t>
+          <t>Aporte Patronal Pasantes</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5544,25 +5544,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5PYG.51110.001</t>
+          <t>5PYG.51070.001</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>200</v>
+        <v>83.33</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Estipendio Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5577,25 +5577,25 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5PYG.51120.001</t>
+          <t>5PYG.51070.002</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>82.72</v>
+        <v>83.33</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Aporte Patronal Pasantes</t>
+          <t>Vacaciones</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
